--- a/mock-data/inventory-master-data.xlsx
+++ b/mock-data/inventory-master-data.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -894,7 +894,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>DC-DET-02</t>
+          <t>DC-CHI-01</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -909,15 +909,15 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>SKU-STL-4520</t>
+          <t>SKU-PMP-7700</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1200</v>
+        <v>8</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>EA</t>
         </is>
       </c>
     </row>
@@ -939,43 +939,73 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>SKU-VLV-2201</t>
+          <t>SKU-STL-4520</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>15</v>
+        <v>1200</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>FT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t>DC-DET-02</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>SKU-VLV-2201</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
           <t>DC-LA-05</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>DC</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>West</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>SKU-STL-4520</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E10" s="4" t="n">
         <v>2000</v>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>FT</t>
         </is>

--- a/mock-data/inventory-master-data.xlsx
+++ b/mock-data/inventory-master-data.xlsx
@@ -530,7 +530,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>PLANT-CHI</t>
+          <t>PLANT-SHB</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -545,7 +545,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>SKU-STL-4520</t>
+          <t>SKU-CTG-4520</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
@@ -553,14 +553,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>EA</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>PLANT-CHI</t>
+          <t>PLANT-SHB</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>SKU-FLG-3010</t>
+          <t>SKU-DRN-3010</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
@@ -590,7 +590,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PLANT-CHI</t>
+          <t>PLANT-SHB</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -620,7 +620,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>PLANT-CHI</t>
+          <t>PLANT-SHB</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>SKU-PMP-7700</t>
+          <t>SKU-SHS-7700</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
@@ -650,7 +650,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>PLANT-CHI</t>
+          <t>PLANT-SHB</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>SKU-GSK-1150</t>
+          <t>SKU-SEL-1150</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
@@ -680,7 +680,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>PLANT-CHI</t>
+          <t>PLANT-SHB</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>SKU-CHM-9100</t>
+          <t>SKU-FIN-9100</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
@@ -789,7 +789,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>SKU-STL-4520</t>
+          <t>SKU-CTG-4520</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
@@ -797,7 +797,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>EA</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>SKU-FLG-3010</t>
+          <t>SKU-DRN-3010</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
@@ -879,7 +879,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>SKU-GSK-1150</t>
+          <t>SKU-SEL-1150</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
@@ -909,7 +909,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>SKU-PMP-7700</t>
+          <t>SKU-SHS-7700</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
@@ -939,7 +939,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>SKU-STL-4520</t>
+          <t>SKU-CTG-4520</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
@@ -947,7 +947,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>EA</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>SKU-STL-4520</t>
+          <t>SKU-CTG-4520</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>EA</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>PLANT-CHI</t>
+          <t>PLANT-SHB</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1108,12 +1108,12 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>SKU-PMP-7700</t>
+          <t>SKU-SHS-7700</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>PLANT-CHI</t>
+          <t>PLANT-SHB</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -1196,7 +1196,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>SKU-STL-4520</t>
+          <t>SKU-CTG-4520</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -1219,7 +1219,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>SKU-FLG-3010</t>
+          <t>SKU-DRN-3010</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
@@ -1265,7 +1265,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>SKU-PMP-7700</t>
+          <t>SKU-SHS-7700</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
@@ -1288,7 +1288,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>SKU-GSK-1150</t>
+          <t>SKU-SEL-1150</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -1311,7 +1311,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>SKU-CHM-9100</t>
+          <t>SKU-FIN-9100</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">

--- a/mock-data/inventory-master-data.xlsx
+++ b/mock-data/inventory-master-data.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -730,6 +730,9 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -770,6 +773,21 @@
           <t>uom</t>
         </is>
       </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>quantity_reserved</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>lead_time_days</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>next_available_date</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -800,6 +818,17 @@
           <t>EA</t>
         </is>
       </c>
+      <c r="G3" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -830,6 +859,17 @@
           <t>EA</t>
         </is>
       </c>
+      <c r="G4" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -860,6 +900,17 @@
           <t>EA</t>
         </is>
       </c>
+      <c r="G5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -890,6 +941,17 @@
           <t>EA</t>
         </is>
       </c>
+      <c r="G6" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -920,6 +982,17 @@
           <t>EA</t>
         </is>
       </c>
+      <c r="G7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -950,6 +1023,17 @@
           <t>EA</t>
         </is>
       </c>
+      <c r="G8" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -980,6 +1064,17 @@
           <t>EA</t>
         </is>
       </c>
+      <c r="G9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1010,10 +1105,21 @@
           <t>EA</t>
         </is>
       </c>
+      <c r="G10" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mock-data/inventory-master-data.xlsx
+++ b/mock-data/inventory-master-data.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1112,6 +1112,88 @@
         <v>4</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>DC-LA-05</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>SKU-DRN-3010</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>DC-LA-05</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>SKU-SEL-1150</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>

--- a/mock-data/inventory-master-data.xlsx
+++ b/mock-data/inventory-master-data.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -575,11 +575,11 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>SKU-DRN-3010</t>
+          <t>SKU-CTG-4600</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
@@ -605,11 +605,11 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>SKU-VLV-2201</t>
+          <t>SKU-CTG-4800</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>60</v>
+        <v>800</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -635,11 +635,11 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>SKU-SHS-7700</t>
+          <t>SKU-DRN-3010</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4</v>
+        <v>800</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
@@ -665,11 +665,11 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>SKU-SEL-1150</t>
+          <t>SKU-VLV-2201</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1500</v>
+        <v>60</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -695,15 +695,135 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
+          <t>SKU-SHS-7700</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>PLANT-SHB</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>PLANT</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>SKU-SEL-1150</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>PLANT-SHB</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>PLANT</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
           <t>SKU-FIN-9100</t>
         </is>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E10" s="4" t="n">
         <v>900</v>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>GAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>PLANT-SHB</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>PLANT</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>SKU-CTG-1017</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>PLANT-SHB</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>PLANT</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>SKU-DRN-7213</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>KIT</t>
         </is>
       </c>
     </row>
@@ -721,7 +841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -848,11 +968,11 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>SKU-DRN-3010</t>
+          <t>SKU-CTG-4600</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>400</v>
+        <v>1500</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
@@ -860,14 +980,14 @@
         </is>
       </c>
       <c r="G4" s="4" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -889,11 +1009,11 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>SKU-VLV-2201</t>
+          <t>SKU-CTG-4800</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -901,14 +1021,14 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-28</t>
         </is>
       </c>
     </row>
@@ -930,11 +1050,11 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>SKU-SEL-1150</t>
+          <t>SKU-DRN-3010</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
@@ -942,14 +1062,14 @@
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
     </row>
@@ -971,11 +1091,11 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>SKU-SHS-7700</t>
+          <t>SKU-VLV-2201</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -983,21 +1103,21 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>DC-DET-02</t>
+          <t>DC-CHI-01</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1012,11 +1132,11 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>SKU-CTG-4520</t>
+          <t>SKU-SEL-1150</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
@@ -1024,21 +1144,21 @@
         </is>
       </c>
       <c r="G8" s="4" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>DC-DET-02</t>
+          <t>DC-CHI-01</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1053,11 +1173,11 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>SKU-VLV-2201</t>
+          <t>SKU-CTG-1017</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>15</v>
+        <v>500</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1065,21 +1185,21 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>DC-LA-05</t>
+          <t>DC-CHI-01</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1089,38 +1209,38 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>SKU-CTG-4520</t>
+          <t>SKU-DRN-7213</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2000</v>
+        <v>60</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>KIT</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>DC-LA-05</t>
+          <t>DC-CHI-01</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1130,16 +1250,16 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>SKU-DRN-3010</t>
+          <t>SKU-SHS-7700</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>200</v>
+        <v>8</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1147,53 +1267,258 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>DC-DET-02</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>SKU-CTG-4520</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>DC-DET-02</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>SKU-VLV-2201</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>DC-DET-02</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>SKU-SHS-7700</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
           <t>DC-LA-05</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>DC</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>West</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>SKU-CTG-4520</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>DC-LA-05</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>SKU-DRN-3010</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>DC-LA-05</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>SKU-SEL-1150</t>
         </is>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E17" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="n">
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="H17" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
@@ -1337,7 +1662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1407,11 +1732,11 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>SKU-DRN-3010</t>
+          <t>SKU-CTG-4600</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1100</v>
+        <v>3200</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -1420,21 +1745,21 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>SKU-VLV-2201</t>
+          <t>SKU-CTG-4800</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>90</v>
+        <v>1200</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -1443,21 +1768,21 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>40</v>
+        <v>600</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>SKU-SHS-7700</t>
+          <t>SKU-DRN-3010</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>5</v>
+        <v>1100</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -1466,21 +1791,21 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>3</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>SKU-SEL-1150</t>
+          <t>SKU-VLV-2201</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2100</v>
+        <v>90</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -1489,34 +1814,126 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>SKU-SHS-7700</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>SKU-SEL-1150</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
           <t>SKU-FIN-9100</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B10" s="4" t="n">
         <v>900</v>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>GAL</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E10" s="4" t="n">
         <v>500</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>SKU-CTG-1017</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SKU-DRN-7213</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>KIT</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
